--- a/SJCE_Benchmark_Graded_Dataset.xlsx
+++ b/SJCE_Benchmark_Graded_Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Pathfinder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF77A01-B49D-40B5-B5A0-DD6926039A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5521AF29-5BDA-4E98-9A12-076842DE7F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,31 +109,31 @@
     <t>Category_12_ROI_Percent_Score</t>
   </si>
   <si>
-    <t>SJCE_Mysore</t>
-  </si>
-  <si>
-    <t>NIE_Mysore</t>
-  </si>
-  <si>
-    <t>NIEIT_Mysore</t>
-  </si>
-  <si>
-    <t>VVCE_Mysore</t>
-  </si>
-  <si>
-    <t>GSSSIETW_Mysore</t>
-  </si>
-  <si>
-    <t>VVIET_Mysore</t>
-  </si>
-  <si>
-    <t>MIT_Mysore</t>
-  </si>
-  <si>
-    <t>ATME_Mysore</t>
-  </si>
-  <si>
-    <t>PESCE_Mandya</t>
+    <t>SJCE, Mysore</t>
+  </si>
+  <si>
+    <t>National Institute of Engineering =,Mysore</t>
+  </si>
+  <si>
+    <t>National Institute of Electronics &amp; Information Technology, Mysore</t>
+  </si>
+  <si>
+    <t>Vidyavardhaka College of Engineering, Mysore</t>
+  </si>
+  <si>
+    <t>GSSS Institute of Engineering &amp; Technology for Women, Mysore</t>
+  </si>
+  <si>
+    <t>Vidya Vikas Institute of Engineering and Technology, Mysore</t>
+  </si>
+  <si>
+    <t>PES College of Engineering, Mandya</t>
+  </si>
+  <si>
+    <t>ATME College of Engineerin, Mysore</t>
+  </si>
+  <si>
+    <t>Maharaja Institute of Technology, Mysore</t>
   </si>
 </sst>
 </file>
@@ -514,7 +514,7 @@
     <col min="15" max="15" width="12.21875" customWidth="1"/>
     <col min="16" max="16" width="10.88671875" customWidth="1"/>
     <col min="17" max="17" width="23.77734375" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="18" max="18" width="23.33203125" customWidth="1"/>
     <col min="19" max="19" width="32.77734375" customWidth="1"/>
     <col min="20" max="20" width="26.5546875" customWidth="1"/>
     <col min="21" max="21" width="29.5546875" customWidth="1"/>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>9.9</v>
